--- a/artfynd/A 15361-2026 artfynd.xlsx
+++ b/artfynd/A 15361-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131106307</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,6 +784,122 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131106306</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601838</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6992935</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0878</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
